--- a/data/trans_bre/P32A-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P32A-Estudios-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,8</t>
+          <t>-2,32; 0,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,36; -1,77</t>
+          <t>-5,58; -1,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 1,29</t>
+          <t>-5,02; 1,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,35; -0,46</t>
+          <t>-6,34; -0,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 98,93</t>
+          <t>-100,0; 78,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 22,98</t>
+          <t>-100,0; 40,86</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,6; -0,17</t>
+          <t>-1,67; -0,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,11</t>
+          <t>-2,85; 0,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,18; -0,15</t>
+          <t>-2,13; -0,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,69</t>
+          <t>-1,18; 1,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 66,33</t>
+          <t>-100,0; 56,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,5; 15,17</t>
+          <t>-82,15; 10,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-92,01; 1,02</t>
+          <t>-89,86; 10,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,15; 240,1</t>
+          <t>-70,13; 226,1</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,89</t>
+          <t>-1,04; 2,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,09</t>
+          <t>-1,22; 1,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,25</t>
+          <t>0,49; 5,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,5</t>
+          <t>-2,01; 1,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-26,26; —</t>
+          <t>-15,39; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-80,9; 190,91</t>
+          <t>-80,27; 165,78</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,33; -0,16</t>
+          <t>-1,32; -0,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,63; -0,72</t>
+          <t>-2,66; -0,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,34</t>
+          <t>-1,6; 0,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,72</t>
+          <t>-1,47; 0,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-92,29; -2,0</t>
+          <t>-93,63; 7,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,56; -24,41</t>
+          <t>-85,83; -25,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,29; 24,56</t>
+          <t>-65,27; 34,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,27; 52,56</t>
+          <t>-66,52; 47,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32A-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P32A-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,34</t>
+          <t>-3,11</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-72,49%</t>
+          <t>-72,43%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,79</t>
+          <t>-2,35; 0,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; -1,87</t>
+          <t>-5,27; -1,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 1,08</t>
+          <t>-4,85; 1,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,34; -0,41</t>
+          <t>-5,87; -0,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 78,36</t>
+          <t>-100,0; 151,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 40,86</t>
+          <t>-100,0; 5,96</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>127,09%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,67; -0,25</t>
+          <t>-1,75; -0,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,11</t>
+          <t>-2,84; 0,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,13; -0,12</t>
+          <t>-2,19; -0,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,71</t>
+          <t>-0,07; 3,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 56,84</t>
+          <t>-100,0; 21,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,15; 10,04</t>
+          <t>-80,33; 10,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-89,86; 10,2</t>
+          <t>-88,3; 1,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,13; 226,1</t>
+          <t>-11,65; 461,88</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-18,56%</t>
+          <t>-21,34%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,04</t>
+          <t>-0,82; 1,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,12</t>
+          <t>-1,2; 1,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,02</t>
+          <t>0,47; 5,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,36</t>
+          <t>-2,31; 1,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,39; —</t>
+          <t>-26,84; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-80,27; 165,78</t>
+          <t>-77,74; 162,59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-22,13%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,32; -0,06</t>
+          <t>-1,32; -0,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; -0,68</t>
+          <t>-2,69; -0,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,52</t>
+          <t>-1,56; 0,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,72</t>
+          <t>-0,81; 1,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-93,63; 7,88</t>
+          <t>-92,11; 2,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,83; -25,68</t>
+          <t>-86,9; -32,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,27; 34,26</t>
+          <t>-66,39; 16,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,52; 47,18</t>
+          <t>-38,03; 122,05</t>
         </is>
       </c>
     </row>
